--- a/Tests/module07_test_cases.xlsx
+++ b/Tests/module07_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test-case-academic-portal\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8CA3FB-8F66-48D9-B919-62F93E314010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A041FF-E2AE-4F8B-A07A-966689414B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
